--- a/data/蜗牛项目-VTS_SSTS_V6.0_ini.xlsx
+++ b/data/蜗牛项目-VTS_SSTS_V6.0_ini.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="857" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="19035" windowHeight="7695" tabRatio="857" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Simple_车型后缀标识_VehSuffix" sheetId="1" r:id="rId1"/>
@@ -14139,13 +14139,13 @@
         <v>43</v>
       </c>
       <c r="E9" s="148">
-        <v>4840</v>
+        <v>4850</v>
       </c>
       <c r="F9" s="144" t="s">
         <v>43</v>
       </c>
       <c r="G9" s="148">
-        <v>4840</v>
+        <v>4850</v>
       </c>
       <c r="H9" s="190"/>
     </row>
@@ -14187,13 +14187,13 @@
         <v>47</v>
       </c>
       <c r="E11" s="148">
-        <v>1560</v>
+        <v>1550</v>
       </c>
       <c r="F11" s="144" t="s">
         <v>47</v>
       </c>
       <c r="G11" s="148">
-        <v>1560</v>
+        <v>1550</v>
       </c>
       <c r="H11" s="190"/>
     </row>
@@ -14211,13 +14211,13 @@
         <v>49</v>
       </c>
       <c r="E12" s="148">
-        <v>2930</v>
+        <v>2950</v>
       </c>
       <c r="F12" s="144" t="s">
         <v>49</v>
       </c>
       <c r="G12" s="148">
-        <v>2930</v>
+        <v>2950</v>
       </c>
       <c r="H12" s="190"/>
     </row>

--- a/data/蜗牛项目-VTS_SSTS_V6.0_ini.xlsx
+++ b/data/蜗牛项目-VTS_SSTS_V6.0_ini.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19035" windowHeight="7695" tabRatio="857" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="19035" windowHeight="7695" tabRatio="857" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Simple_车型后缀标识_VehSuffix" sheetId="1" r:id="rId1"/>
@@ -2049,7 +2049,7 @@
     <t>机械内阻参数</t>
   </si>
   <si>
-    <t>前制动钳总成内阻</t>
+    <t>前制动钳阻力矩</t>
   </si>
   <si>
     <t>Nm</t>
@@ -2058,19 +2058,19 @@
     <t>F_Brake_Res</t>
   </si>
   <si>
-    <t>后制动钳总成内阻</t>
+    <t>后制动钳阻力矩</t>
   </si>
   <si>
     <t>R_Brake_Res</t>
   </si>
   <si>
-    <t>前轮毂轴承内阻</t>
+    <t>前轮毂轴承阻力矩</t>
   </si>
   <si>
     <t>F_Bearing_Res</t>
   </si>
   <si>
-    <t>后轮毂轴承内阻</t>
+    <t>后轮毂轴承阻力矩</t>
   </si>
   <si>
     <t>R_Bearing_Res</t>
@@ -4317,7 +4317,7 @@
     <xf numFmtId="176" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="193">
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4730,6 +4730,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="53" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="62" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="53" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -13865,7 +13868,7 @@
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="181" t="s">
+      <c r="B1" s="182" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="24" t="s">
@@ -13885,7 +13888,7 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="156" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="144" t="s">
@@ -13908,7 +13911,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="155" t="s">
+      <c r="A3" s="156" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="144" t="s">
@@ -13960,16 +13963,16 @@
       <c r="B1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="178" t="s">
+      <c r="C1" s="179" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="179" t="s">
+      <c r="D1" s="180" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="13"/>
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
-      <c r="H1" s="180" t="s">
+      <c r="H1" s="181" t="s">
         <v>6</v>
       </c>
     </row>
@@ -13977,7 +13980,7 @@
       <c r="A2" s="22"/>
       <c r="B2" s="17"/>
       <c r="C2" s="18"/>
-      <c r="D2" s="181" t="s">
+      <c r="D2" s="182" t="s">
         <v>22</v>
       </c>
       <c r="E2" s="3"/>
@@ -13985,28 +13988,28 @@
         <v>23</v>
       </c>
       <c r="G2" s="3"/>
-      <c r="H2" s="182"/>
+      <c r="H2" s="183"/>
     </row>
     <row r="3" customFormat="1" ht="15" customHeight="1" spans="1:8">
       <c r="A3" s="29"/>
       <c r="B3" s="26"/>
-      <c r="C3" s="183"/>
-      <c r="D3" s="184" t="s">
+      <c r="C3" s="184"/>
+      <c r="D3" s="185" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="185" t="s">
+      <c r="E3" s="186" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="185" t="s">
+      <c r="F3" s="186" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="186" t="s">
+      <c r="G3" s="187" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="187"/>
+      <c r="H3" s="188"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="188">
+      <c r="A4" s="189">
         <v>1</v>
       </c>
       <c r="B4" s="139" t="s">
@@ -14027,10 +14030,10 @@
       <c r="G4" s="138" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="189"/>
+      <c r="H4" s="190"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="188">
+      <c r="A5" s="189">
         <v>2</v>
       </c>
       <c r="B5" s="139" t="s">
@@ -14051,10 +14054,10 @@
       <c r="G5" s="138" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="189"/>
+      <c r="H5" s="190"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="188">
+      <c r="A6" s="189">
         <v>3</v>
       </c>
       <c r="B6" s="139" t="s">
@@ -14075,13 +14078,13 @@
       <c r="G6" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="189"/>
+      <c r="H6" s="190"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="188">
+      <c r="A7" s="189">
         <v>4</v>
       </c>
-      <c r="B7" s="155" t="s">
+      <c r="B7" s="156" t="s">
         <v>34</v>
       </c>
       <c r="C7" s="141" t="s">
@@ -14099,13 +14102,13 @@
       <c r="G7" s="148" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="190"/>
+      <c r="H7" s="191"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="188">
+      <c r="A8" s="189">
         <v>5</v>
       </c>
-      <c r="B8" s="155" t="s">
+      <c r="B8" s="156" t="s">
         <v>37</v>
       </c>
       <c r="C8" s="141" t="s">
@@ -14123,13 +14126,13 @@
       <c r="G8" s="148" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="190"/>
+      <c r="H8" s="191"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="188">
+      <c r="A9" s="189">
         <v>6</v>
       </c>
-      <c r="B9" s="155" t="s">
+      <c r="B9" s="156" t="s">
         <v>41</v>
       </c>
       <c r="C9" s="141" t="s">
@@ -14147,13 +14150,13 @@
       <c r="G9" s="148">
         <v>4850</v>
       </c>
-      <c r="H9" s="190"/>
+      <c r="H9" s="191"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="188">
+      <c r="A10" s="189">
         <v>7</v>
       </c>
-      <c r="B10" s="155" t="s">
+      <c r="B10" s="156" t="s">
         <v>44</v>
       </c>
       <c r="C10" s="141" t="s">
@@ -14171,13 +14174,13 @@
       <c r="G10" s="148">
         <v>1950</v>
       </c>
-      <c r="H10" s="190"/>
+      <c r="H10" s="191"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="188">
+      <c r="A11" s="189">
         <v>8</v>
       </c>
-      <c r="B11" s="155" t="s">
+      <c r="B11" s="156" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="141" t="s">
@@ -14195,13 +14198,13 @@
       <c r="G11" s="148">
         <v>1550</v>
       </c>
-      <c r="H11" s="190"/>
+      <c r="H11" s="191"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="188">
+      <c r="A12" s="189">
         <v>9</v>
       </c>
-      <c r="B12" s="155" t="s">
+      <c r="B12" s="156" t="s">
         <v>48</v>
       </c>
       <c r="C12" s="141" t="s">
@@ -14219,13 +14222,13 @@
       <c r="G12" s="148">
         <v>2950</v>
       </c>
-      <c r="H12" s="190"/>
+      <c r="H12" s="191"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="188">
+      <c r="A13" s="189">
         <v>10</v>
       </c>
-      <c r="B13" s="155" t="s">
+      <c r="B13" s="156" t="s">
         <v>50</v>
       </c>
       <c r="C13" s="141" t="s">
@@ -14243,13 +14246,13 @@
       <c r="G13" s="148">
         <v>5</v>
       </c>
-      <c r="H13" s="190"/>
+      <c r="H13" s="191"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="188">
+      <c r="A14" s="189">
         <v>11</v>
       </c>
-      <c r="B14" s="155" t="s">
+      <c r="B14" s="156" t="s">
         <v>53</v>
       </c>
       <c r="C14" s="141" t="s">
@@ -14267,13 +14270,13 @@
       <c r="G14" s="148" t="s">
         <v>55</v>
       </c>
-      <c r="H14" s="190"/>
+      <c r="H14" s="191"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="188">
+      <c r="A15" s="189">
         <v>12</v>
       </c>
-      <c r="B15" s="155" t="s">
+      <c r="B15" s="156" t="s">
         <v>56</v>
       </c>
       <c r="C15" s="141" t="s">
@@ -14291,13 +14294,13 @@
       <c r="G15" s="148" t="s">
         <v>58</v>
       </c>
-      <c r="H15" s="190"/>
+      <c r="H15" s="191"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="188">
+      <c r="A16" s="189">
         <v>13</v>
       </c>
-      <c r="B16" s="155" t="s">
+      <c r="B16" s="156" t="s">
         <v>59</v>
       </c>
       <c r="C16" s="141" t="s">
@@ -14315,13 +14318,13 @@
       <c r="G16" s="148" t="s">
         <v>63</v>
       </c>
-      <c r="H16" s="190"/>
+      <c r="H16" s="191"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="188">
+      <c r="A17" s="189">
         <v>14</v>
       </c>
-      <c r="B17" s="155" t="s">
+      <c r="B17" s="156" t="s">
         <v>64</v>
       </c>
       <c r="C17" s="141" t="s">
@@ -14339,13 +14342,13 @@
       <c r="G17" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="H17" s="190"/>
+      <c r="H17" s="191"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="188">
+      <c r="A18" s="189">
         <v>15</v>
       </c>
-      <c r="B18" s="155" t="s">
+      <c r="B18" s="156" t="s">
         <v>67</v>
       </c>
       <c r="C18" s="131" t="s">
@@ -14363,13 +14366,13 @@
       <c r="G18" s="148" t="s">
         <v>69</v>
       </c>
-      <c r="H18" s="190"/>
+      <c r="H18" s="191"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="188">
+      <c r="A19" s="189">
         <v>16</v>
       </c>
-      <c r="B19" s="155" t="s">
+      <c r="B19" s="156" t="s">
         <v>71</v>
       </c>
       <c r="C19" s="141" t="s">
@@ -14387,13 +14390,13 @@
       <c r="G19" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="H19" s="190"/>
+      <c r="H19" s="191"/>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:8">
-      <c r="A20" s="188">
+      <c r="A20" s="189">
         <v>17</v>
       </c>
-      <c r="B20" s="173" t="s">
+      <c r="B20" s="174" t="s">
         <v>74</v>
       </c>
       <c r="C20" s="34" t="s">
@@ -14402,16 +14405,16 @@
       <c r="D20" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="E20" s="175" t="s">
+      <c r="E20" s="176" t="s">
         <v>73</v>
       </c>
       <c r="F20" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="G20" s="175" t="s">
+      <c r="G20" s="176" t="s">
         <v>73</v>
       </c>
-      <c r="H20" s="191"/>
+      <c r="H20" s="192"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -15064,7 +15067,7 @@
       </c>
       <c r="B15" s="17"/>
       <c r="C15" s="26"/>
-      <c r="D15" s="149" t="s">
+      <c r="D15" s="152" t="s">
         <v>113</v>
       </c>
       <c r="E15" s="141">
@@ -15096,7 +15099,7 @@
       <c r="Q15" s="148">
         <v>0</v>
       </c>
-      <c r="R15" s="152" t="s">
+      <c r="R15" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S15" s="145"/>
@@ -15276,7 +15279,7 @@
       <c r="Q19" s="148">
         <v>0</v>
       </c>
-      <c r="R19" s="152" t="s">
+      <c r="R19" s="153" t="s">
         <v>126</v>
       </c>
       <c r="S19" s="145"/>
@@ -15321,7 +15324,7 @@
       <c r="Q20" s="138">
         <v>0</v>
       </c>
-      <c r="R20" s="152" t="s">
+      <c r="R20" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S20" s="145"/>
@@ -15336,7 +15339,7 @@
       <c r="C21" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="D21" s="153" t="s">
+      <c r="D21" s="154" t="s">
         <v>130</v>
       </c>
       <c r="E21" s="147" t="s">
@@ -15368,7 +15371,7 @@
       <c r="Q21" s="148">
         <v>0</v>
       </c>
-      <c r="R21" s="152" t="s">
+      <c r="R21" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S21" s="145"/>
@@ -15381,7 +15384,7 @@
       </c>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
-      <c r="D22" s="153" t="s">
+      <c r="D22" s="154" t="s">
         <v>132</v>
       </c>
       <c r="E22" s="147" t="s">
@@ -15413,7 +15416,7 @@
       <c r="Q22" s="138">
         <v>0</v>
       </c>
-      <c r="R22" s="152" t="s">
+      <c r="R22" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S22" s="145"/>
@@ -15426,7 +15429,7 @@
       </c>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
-      <c r="D23" s="153" t="s">
+      <c r="D23" s="154" t="s">
         <v>135</v>
       </c>
       <c r="E23" s="147" t="s">
@@ -15458,7 +15461,7 @@
       <c r="Q23" s="148">
         <v>0</v>
       </c>
-      <c r="R23" s="152" t="s">
+      <c r="R23" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S23" s="145"/>
@@ -15471,7 +15474,7 @@
       </c>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
-      <c r="D24" s="154" t="s">
+      <c r="D24" s="155" t="s">
         <v>137</v>
       </c>
       <c r="E24" s="147" t="s">
@@ -15503,7 +15506,7 @@
       <c r="Q24" s="138">
         <v>0</v>
       </c>
-      <c r="R24" s="152" t="s">
+      <c r="R24" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S24" s="145"/>
@@ -15516,7 +15519,7 @@
       </c>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
-      <c r="D25" s="153" t="s">
+      <c r="D25" s="154" t="s">
         <v>140</v>
       </c>
       <c r="E25" s="147" t="s">
@@ -15548,7 +15551,7 @@
       <c r="Q25" s="148">
         <v>0</v>
       </c>
-      <c r="R25" s="152" t="s">
+      <c r="R25" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S25" s="145"/>
@@ -15561,7 +15564,7 @@
       </c>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
-      <c r="D26" s="153" t="s">
+      <c r="D26" s="154" t="s">
         <v>142</v>
       </c>
       <c r="E26" s="147" t="s">
@@ -15593,7 +15596,7 @@
       <c r="Q26" s="138">
         <v>0</v>
       </c>
-      <c r="R26" s="152" t="s">
+      <c r="R26" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S26" s="145"/>
@@ -15606,7 +15609,7 @@
       </c>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
-      <c r="D27" s="153" t="s">
+      <c r="D27" s="154" t="s">
         <v>144</v>
       </c>
       <c r="E27" s="147" t="s">
@@ -15638,7 +15641,7 @@
       <c r="Q27" s="148">
         <v>0</v>
       </c>
-      <c r="R27" s="152" t="s">
+      <c r="R27" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S27" s="145"/>
@@ -15651,7 +15654,7 @@
       </c>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
-      <c r="D28" s="154" t="s">
+      <c r="D28" s="155" t="s">
         <v>146</v>
       </c>
       <c r="E28" s="147" t="s">
@@ -15683,7 +15686,7 @@
       <c r="Q28" s="138">
         <v>0</v>
       </c>
-      <c r="R28" s="152" t="s">
+      <c r="R28" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S28" s="145"/>
@@ -15696,7 +15699,7 @@
       </c>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
-      <c r="D29" s="154" t="s">
+      <c r="D29" s="155" t="s">
         <v>148</v>
       </c>
       <c r="E29" s="147">
@@ -15728,7 +15731,7 @@
       <c r="Q29" s="148">
         <v>0</v>
       </c>
-      <c r="R29" s="152" t="s">
+      <c r="R29" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S29" s="145"/>
@@ -15741,7 +15744,7 @@
       </c>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
-      <c r="D30" s="154" t="s">
+      <c r="D30" s="155" t="s">
         <v>150</v>
       </c>
       <c r="E30" s="147">
@@ -15773,7 +15776,7 @@
       <c r="Q30" s="138">
         <v>0</v>
       </c>
-      <c r="R30" s="152" t="s">
+      <c r="R30" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S30" s="145"/>
@@ -15786,7 +15789,7 @@
       </c>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
-      <c r="D31" s="154" t="s">
+      <c r="D31" s="155" t="s">
         <v>152</v>
       </c>
       <c r="E31" s="147" t="s">
@@ -15831,7 +15834,7 @@
       </c>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
-      <c r="D32" s="154" t="s">
+      <c r="D32" s="155" t="s">
         <v>155</v>
       </c>
       <c r="E32" s="147" t="s">
@@ -15876,7 +15879,7 @@
       </c>
       <c r="B33" s="17"/>
       <c r="C33" s="26"/>
-      <c r="D33" s="154" t="s">
+      <c r="D33" s="155" t="s">
         <v>158</v>
       </c>
       <c r="E33" s="147" t="s">
@@ -15923,7 +15926,7 @@
       <c r="C34" s="113" t="s">
         <v>161</v>
       </c>
-      <c r="D34" s="155" t="s">
+      <c r="D34" s="156" t="s">
         <v>162</v>
       </c>
       <c r="E34" s="147" t="s">
@@ -15955,7 +15958,7 @@
       <c r="Q34" s="148">
         <v>0</v>
       </c>
-      <c r="R34" s="152" t="s">
+      <c r="R34" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S34" s="145"/>
@@ -15968,7 +15971,7 @@
       </c>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
-      <c r="D35" s="155" t="s">
+      <c r="D35" s="156" t="s">
         <v>164</v>
       </c>
       <c r="E35" s="147" t="s">
@@ -16000,7 +16003,7 @@
       <c r="Q35" s="138">
         <v>0</v>
       </c>
-      <c r="R35" s="152" t="s">
+      <c r="R35" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S35" s="145"/>
@@ -16013,7 +16016,7 @@
       </c>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
-      <c r="D36" s="155" t="s">
+      <c r="D36" s="156" t="s">
         <v>166</v>
       </c>
       <c r="E36" s="147" t="s">
@@ -16045,7 +16048,7 @@
       <c r="Q36" s="148">
         <v>0</v>
       </c>
-      <c r="R36" s="152" t="s">
+      <c r="R36" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S36" s="145"/>
@@ -16058,7 +16061,7 @@
       </c>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
-      <c r="D37" s="155" t="s">
+      <c r="D37" s="156" t="s">
         <v>168</v>
       </c>
       <c r="E37" s="147" t="s">
@@ -16090,7 +16093,7 @@
       <c r="Q37" s="138">
         <v>0</v>
       </c>
-      <c r="R37" s="152" t="s">
+      <c r="R37" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S37" s="145"/>
@@ -16103,7 +16106,7 @@
       </c>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
-      <c r="D38" s="155" t="s">
+      <c r="D38" s="156" t="s">
         <v>171</v>
       </c>
       <c r="E38" s="147">
@@ -16135,7 +16138,7 @@
       <c r="Q38" s="148">
         <v>0</v>
       </c>
-      <c r="R38" s="152" t="s">
+      <c r="R38" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S38" s="145"/>
@@ -16148,7 +16151,7 @@
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
-      <c r="D39" s="155" t="s">
+      <c r="D39" s="156" t="s">
         <v>173</v>
       </c>
       <c r="E39" s="147">
@@ -16180,7 +16183,7 @@
       <c r="Q39" s="138">
         <v>0</v>
       </c>
-      <c r="R39" s="152" t="s">
+      <c r="R39" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S39" s="145"/>
@@ -16195,7 +16198,7 @@
       </c>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
-      <c r="D40" s="149" t="s">
+      <c r="D40" s="152" t="s">
         <v>176</v>
       </c>
       <c r="E40" s="147">
@@ -16221,7 +16224,7 @@
       <c r="Q40" s="148">
         <v>0</v>
       </c>
-      <c r="R40" s="152" t="s">
+      <c r="R40" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S40" s="145"/>
@@ -16234,7 +16237,7 @@
       </c>
       <c r="B41" s="17"/>
       <c r="C41" s="26"/>
-      <c r="D41" s="149" t="s">
+      <c r="D41" s="152" t="s">
         <v>178</v>
       </c>
       <c r="E41" s="147">
@@ -16260,7 +16263,7 @@
       <c r="Q41" s="138">
         <v>0</v>
       </c>
-      <c r="R41" s="152" t="s">
+      <c r="R41" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S41" s="145"/>
@@ -16275,7 +16278,7 @@
       <c r="C42" s="113" t="s">
         <v>180</v>
       </c>
-      <c r="D42" s="155" t="s">
+      <c r="D42" s="156" t="s">
         <v>181</v>
       </c>
       <c r="E42" s="147" t="s">
@@ -16314,7 +16317,7 @@
       </c>
       <c r="B43" s="17"/>
       <c r="C43" s="26"/>
-      <c r="D43" s="155" t="s">
+      <c r="D43" s="156" t="s">
         <v>184</v>
       </c>
       <c r="E43" s="147" t="s">
@@ -16338,7 +16341,7 @@
       <c r="O43" s="145"/>
       <c r="P43" s="145"/>
       <c r="Q43" s="138"/>
-      <c r="R43" s="152" t="s">
+      <c r="R43" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S43" s="145"/>
@@ -16353,7 +16356,7 @@
       <c r="C44" s="113" t="s">
         <v>187</v>
       </c>
-      <c r="D44" s="155" t="s">
+      <c r="D44" s="156" t="s">
         <v>188</v>
       </c>
       <c r="E44" s="147" t="s">
@@ -16377,7 +16380,7 @@
       <c r="O44" s="145"/>
       <c r="P44" s="145"/>
       <c r="Q44" s="148"/>
-      <c r="R44" s="152" t="s">
+      <c r="R44" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S44" s="145"/>
@@ -16392,7 +16395,7 @@
       <c r="C45" s="113" t="s">
         <v>191</v>
       </c>
-      <c r="D45" s="154" t="s">
+      <c r="D45" s="155" t="s">
         <v>192</v>
       </c>
       <c r="E45" s="147" t="s">
@@ -16439,7 +16442,7 @@
       </c>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
-      <c r="D46" s="154" t="s">
+      <c r="D46" s="155" t="s">
         <v>195</v>
       </c>
       <c r="E46" s="147" t="s">
@@ -16486,7 +16489,7 @@
       </c>
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
-      <c r="D47" s="154" t="s">
+      <c r="D47" s="155" t="s">
         <v>197</v>
       </c>
       <c r="E47" s="147" t="s">
@@ -16533,7 +16536,7 @@
       </c>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
-      <c r="D48" s="154" t="s">
+      <c r="D48" s="155" t="s">
         <v>199</v>
       </c>
       <c r="E48" s="147">
@@ -16565,7 +16568,7 @@
       <c r="Q48" s="148">
         <v>0</v>
       </c>
-      <c r="R48" s="152" t="s">
+      <c r="R48" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S48" s="145"/>
@@ -16578,7 +16581,7 @@
       </c>
       <c r="B49" s="17"/>
       <c r="C49" s="26"/>
-      <c r="D49" s="154" t="s">
+      <c r="D49" s="155" t="s">
         <v>201</v>
       </c>
       <c r="E49" s="147">
@@ -16610,7 +16613,7 @@
       <c r="Q49" s="138">
         <v>0</v>
       </c>
-      <c r="R49" s="152" t="s">
+      <c r="R49" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S49" s="145"/>
@@ -16625,7 +16628,7 @@
       <c r="C50" s="113" t="s">
         <v>203</v>
       </c>
-      <c r="D50" s="154" t="s">
+      <c r="D50" s="155" t="s">
         <v>204</v>
       </c>
       <c r="E50" s="147">
@@ -16672,7 +16675,7 @@
       <c r="C51" s="113" t="s">
         <v>206</v>
       </c>
-      <c r="D51" s="155" t="s">
+      <c r="D51" s="156" t="s">
         <v>207</v>
       </c>
       <c r="E51" s="141">
@@ -16704,7 +16707,7 @@
       <c r="Q51" s="138">
         <v>0</v>
       </c>
-      <c r="R51" s="152" t="s">
+      <c r="R51" s="153" t="s">
         <v>115</v>
       </c>
       <c r="S51" s="145"/>
@@ -16721,7 +16724,7 @@
       <c r="C52" s="113" t="s">
         <v>210</v>
       </c>
-      <c r="D52" s="155" t="s">
+      <c r="D52" s="156" t="s">
         <v>211</v>
       </c>
       <c r="E52" s="141" t="s">
@@ -16760,7 +16763,7 @@
       </c>
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
-      <c r="D53" s="149" t="s">
+      <c r="D53" s="152" t="s">
         <v>213</v>
       </c>
       <c r="E53" s="141" t="s">
@@ -16799,27 +16802,27 @@
       </c>
       <c r="B54" s="26"/>
       <c r="C54" s="26"/>
-      <c r="D54" s="156" t="s">
+      <c r="D54" s="157" t="s">
         <v>215</v>
       </c>
-      <c r="E54" s="157" t="s">
+      <c r="E54" s="158" t="s">
         <v>193</v>
       </c>
-      <c r="F54" s="158"/>
-      <c r="G54" s="159"/>
-      <c r="H54" s="160"/>
-      <c r="I54" s="161"/>
-      <c r="J54" s="162"/>
+      <c r="F54" s="159"/>
+      <c r="G54" s="160"/>
+      <c r="H54" s="161"/>
+      <c r="I54" s="162"/>
+      <c r="J54" s="163"/>
       <c r="K54" s="147"/>
-      <c r="L54" s="158" t="s">
+      <c r="L54" s="159" t="s">
         <v>216</v>
       </c>
-      <c r="M54" s="159"/>
-      <c r="N54" s="160" t="s">
+      <c r="M54" s="160"/>
+      <c r="N54" s="161" t="s">
         <v>216</v>
       </c>
-      <c r="O54" s="161"/>
-      <c r="P54" s="162" t="s">
+      <c r="O54" s="162"/>
+      <c r="P54" s="163" t="s">
         <v>216</v>
       </c>
       <c r="Q54" s="148">
@@ -16828,21 +16831,21 @@
       <c r="R54" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="S54" s="161"/>
-      <c r="T54" s="161"/>
-      <c r="U54" s="163"/>
+      <c r="S54" s="162"/>
+      <c r="T54" s="162"/>
+      <c r="U54" s="164"/>
     </row>
     <row r="55" spans="1:21">
       <c r="A55" s="129">
         <v>51</v>
       </c>
-      <c r="B55" s="164" t="s">
+      <c r="B55" s="165" t="s">
         <v>217</v>
       </c>
-      <c r="C55" s="165" t="s">
+      <c r="C55" s="166" t="s">
         <v>86</v>
       </c>
-      <c r="D55" s="166" t="s">
+      <c r="D55" s="167" t="s">
         <v>218</v>
       </c>
       <c r="E55" s="48" t="s">
@@ -16864,14 +16867,14 @@
       <c r="M55" s="50">
         <v>425</v>
       </c>
-      <c r="N55" s="167"/>
+      <c r="N55" s="168"/>
       <c r="O55" s="52"/>
       <c r="P55" s="53"/>
       <c r="Q55" s="55"/>
-      <c r="R55" s="168"/>
+      <c r="R55" s="169"/>
       <c r="S55" s="52"/>
       <c r="T55" s="52"/>
-      <c r="U55" s="169"/>
+      <c r="U55" s="170"/>
     </row>
     <row r="56" spans="1:21">
       <c r="A56" s="129">
@@ -16879,7 +16882,7 @@
       </c>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
-      <c r="D56" s="155" t="s">
+      <c r="D56" s="156" t="s">
         <v>220</v>
       </c>
       <c r="E56" s="141" t="s">
@@ -16905,10 +16908,10 @@
       <c r="O56" s="145"/>
       <c r="P56" s="146"/>
       <c r="Q56" s="148"/>
-      <c r="R56" s="152"/>
+      <c r="R56" s="153"/>
       <c r="S56" s="145"/>
       <c r="T56" s="145"/>
-      <c r="U56" s="170"/>
+      <c r="U56" s="171"/>
     </row>
     <row r="57" spans="1:21">
       <c r="A57" s="129">
@@ -16916,7 +16919,7 @@
       </c>
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
-      <c r="D57" s="155" t="s">
+      <c r="D57" s="156" t="s">
         <v>48</v>
       </c>
       <c r="E57" s="141" t="s">
@@ -16942,10 +16945,10 @@
       <c r="O57" s="145"/>
       <c r="P57" s="146"/>
       <c r="Q57" s="148"/>
-      <c r="R57" s="152"/>
+      <c r="R57" s="153"/>
       <c r="S57" s="145"/>
       <c r="T57" s="145"/>
-      <c r="U57" s="170"/>
+      <c r="U57" s="171"/>
     </row>
     <row r="58" spans="1:21">
       <c r="A58" s="129">
@@ -16953,7 +16956,7 @@
       </c>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
-      <c r="D58" s="155" t="s">
+      <c r="D58" s="156" t="s">
         <v>224</v>
       </c>
       <c r="E58" s="141" t="s">
@@ -16979,10 +16982,10 @@
       <c r="O58" s="145"/>
       <c r="P58" s="146"/>
       <c r="Q58" s="148"/>
-      <c r="R58" s="152"/>
+      <c r="R58" s="153"/>
       <c r="S58" s="145"/>
       <c r="T58" s="145"/>
-      <c r="U58" s="170"/>
+      <c r="U58" s="171"/>
     </row>
     <row r="59" spans="1:21">
       <c r="A59" s="129">
@@ -16990,7 +16993,7 @@
       </c>
       <c r="B59" s="17"/>
       <c r="C59" s="26"/>
-      <c r="D59" s="155" t="s">
+      <c r="D59" s="156" t="s">
         <v>226</v>
       </c>
       <c r="E59" s="141" t="s">
@@ -17016,20 +17019,20 @@
       <c r="O59" s="145"/>
       <c r="P59" s="146"/>
       <c r="Q59" s="148"/>
-      <c r="R59" s="152"/>
+      <c r="R59" s="153"/>
       <c r="S59" s="145"/>
       <c r="T59" s="145"/>
-      <c r="U59" s="170"/>
+      <c r="U59" s="171"/>
     </row>
     <row r="60" spans="1:21">
       <c r="A60" s="129">
         <v>56</v>
       </c>
       <c r="B60" s="17"/>
-      <c r="C60" s="171" t="s">
+      <c r="C60" s="172" t="s">
         <v>228</v>
       </c>
-      <c r="D60" s="155" t="s">
+      <c r="D60" s="156" t="s">
         <v>229</v>
       </c>
       <c r="E60" s="141" t="s">
@@ -17055,10 +17058,10 @@
       <c r="O60" s="145"/>
       <c r="P60" s="146"/>
       <c r="Q60" s="148"/>
-      <c r="R60" s="152"/>
+      <c r="R60" s="153"/>
       <c r="S60" s="145"/>
       <c r="T60" s="145"/>
-      <c r="U60" s="170" t="s">
+      <c r="U60" s="171" t="s">
         <v>232</v>
       </c>
     </row>
@@ -17068,7 +17071,7 @@
       </c>
       <c r="B61" s="17"/>
       <c r="C61" s="17"/>
-      <c r="D61" s="155" t="s">
+      <c r="D61" s="156" t="s">
         <v>233</v>
       </c>
       <c r="E61" s="141" t="s">
@@ -17090,10 +17093,10 @@
       <c r="O61" s="145"/>
       <c r="P61" s="146"/>
       <c r="Q61" s="148"/>
-      <c r="R61" s="152"/>
+      <c r="R61" s="153"/>
       <c r="S61" s="145"/>
       <c r="T61" s="145"/>
-      <c r="U61" s="170"/>
+      <c r="U61" s="171"/>
     </row>
     <row r="62" spans="1:21">
       <c r="A62" s="129">
@@ -17101,7 +17104,7 @@
       </c>
       <c r="B62" s="17"/>
       <c r="C62" s="26"/>
-      <c r="D62" s="155" t="s">
+      <c r="D62" s="156" t="s">
         <v>235</v>
       </c>
       <c r="E62" s="141" t="s">
@@ -17123,20 +17126,20 @@
       <c r="O62" s="145"/>
       <c r="P62" s="146"/>
       <c r="Q62" s="148"/>
-      <c r="R62" s="152"/>
+      <c r="R62" s="153"/>
       <c r="S62" s="145"/>
       <c r="T62" s="145"/>
-      <c r="U62" s="170"/>
+      <c r="U62" s="171"/>
     </row>
     <row r="63" spans="1:21">
       <c r="A63" s="129">
         <v>59</v>
       </c>
       <c r="B63" s="17"/>
-      <c r="C63" s="171" t="s">
+      <c r="C63" s="172" t="s">
         <v>237</v>
       </c>
-      <c r="D63" s="155" t="s">
+      <c r="D63" s="156" t="s">
         <v>238</v>
       </c>
       <c r="E63" s="141" t="s">
@@ -17162,20 +17165,20 @@
       <c r="O63" s="145"/>
       <c r="P63" s="146"/>
       <c r="Q63" s="148"/>
-      <c r="R63" s="152"/>
+      <c r="R63" s="153"/>
       <c r="S63" s="145"/>
       <c r="T63" s="145"/>
-      <c r="U63" s="170"/>
+      <c r="U63" s="171"/>
     </row>
     <row r="64" spans="1:21">
       <c r="A64" s="129">
         <v>60</v>
       </c>
       <c r="B64" s="17"/>
-      <c r="C64" s="171" t="s">
+      <c r="C64" s="172" t="s">
         <v>240</v>
       </c>
-      <c r="D64" s="155" t="s">
+      <c r="D64" s="156" t="s">
         <v>241</v>
       </c>
       <c r="E64" s="141" t="s">
@@ -17201,10 +17204,10 @@
       <c r="O64" s="145"/>
       <c r="P64" s="146"/>
       <c r="Q64" s="148"/>
-      <c r="R64" s="152"/>
+      <c r="R64" s="153"/>
       <c r="S64" s="145"/>
       <c r="T64" s="145"/>
-      <c r="U64" s="170"/>
+      <c r="U64" s="171"/>
     </row>
     <row r="65" spans="1:27">
       <c r="A65" s="129">
@@ -17212,7 +17215,7 @@
       </c>
       <c r="B65" s="17"/>
       <c r="C65" s="17"/>
-      <c r="D65" s="155" t="s">
+      <c r="D65" s="156" t="s">
         <v>244</v>
       </c>
       <c r="E65" s="141" t="s">
@@ -17238,10 +17241,10 @@
       <c r="O65" s="145"/>
       <c r="P65" s="146"/>
       <c r="Q65" s="148"/>
-      <c r="R65" s="152"/>
+      <c r="R65" s="153"/>
       <c r="S65" s="145"/>
       <c r="T65" s="145"/>
-      <c r="U65" s="170"/>
+      <c r="U65" s="171"/>
     </row>
     <row r="66" spans="1:27">
       <c r="A66" s="129">
@@ -17249,7 +17252,7 @@
       </c>
       <c r="B66" s="17"/>
       <c r="C66" s="26"/>
-      <c r="D66" s="155" t="s">
+      <c r="D66" s="156" t="s">
         <v>246</v>
       </c>
       <c r="E66" s="141">
@@ -17275,10 +17278,10 @@
       <c r="O66" s="145"/>
       <c r="P66" s="146"/>
       <c r="Q66" s="148"/>
-      <c r="R66" s="152"/>
+      <c r="R66" s="153"/>
       <c r="S66" s="145"/>
       <c r="T66" s="145"/>
-      <c r="U66" s="170"/>
+      <c r="U66" s="171"/>
       <c r="AA66" t="s">
         <v>250</v>
       </c>
@@ -17288,10 +17291,10 @@
         <v>63</v>
       </c>
       <c r="B67" s="17"/>
-      <c r="C67" s="171" t="s">
+      <c r="C67" s="172" t="s">
         <v>251</v>
       </c>
-      <c r="D67" s="155" t="s">
+      <c r="D67" s="156" t="s">
         <v>252</v>
       </c>
       <c r="E67" s="141">
@@ -17317,10 +17320,10 @@
       <c r="O67" s="145"/>
       <c r="P67" s="146"/>
       <c r="Q67" s="148"/>
-      <c r="R67" s="152"/>
+      <c r="R67" s="153"/>
       <c r="S67" s="145"/>
       <c r="T67" s="145"/>
-      <c r="U67" s="170"/>
+      <c r="U67" s="171"/>
     </row>
     <row r="68" spans="1:27">
       <c r="A68" s="129">
@@ -17328,7 +17331,7 @@
       </c>
       <c r="B68" s="17"/>
       <c r="C68" s="26"/>
-      <c r="D68" s="155" t="s">
+      <c r="D68" s="156" t="s">
         <v>254</v>
       </c>
       <c r="E68" s="141">
@@ -17354,20 +17357,20 @@
       <c r="O68" s="145"/>
       <c r="P68" s="146"/>
       <c r="Q68" s="148"/>
-      <c r="R68" s="152"/>
+      <c r="R68" s="153"/>
       <c r="S68" s="145"/>
       <c r="T68" s="145"/>
-      <c r="U68" s="170"/>
+      <c r="U68" s="171"/>
     </row>
     <row r="69" spans="1:27">
       <c r="A69" s="129">
         <v>65</v>
       </c>
       <c r="B69" s="17"/>
-      <c r="C69" s="172" t="s">
+      <c r="C69" s="173" t="s">
         <v>256</v>
       </c>
-      <c r="D69" s="155" t="s">
+      <c r="D69" s="156" t="s">
         <v>257</v>
       </c>
       <c r="E69" s="141">
@@ -17393,10 +17396,10 @@
       <c r="O69" s="145"/>
       <c r="P69" s="146"/>
       <c r="Q69" s="148"/>
-      <c r="R69" s="152"/>
+      <c r="R69" s="153"/>
       <c r="S69" s="145"/>
       <c r="T69" s="145"/>
-      <c r="U69" s="170"/>
+      <c r="U69" s="171"/>
     </row>
     <row r="70" spans="1:27">
       <c r="A70" s="129">
@@ -17404,7 +17407,7 @@
       </c>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
-      <c r="D70" s="155" t="s">
+      <c r="D70" s="156" t="s">
         <v>259</v>
       </c>
       <c r="E70" s="141">
@@ -17430,10 +17433,10 @@
       <c r="O70" s="145"/>
       <c r="P70" s="146"/>
       <c r="Q70" s="148"/>
-      <c r="R70" s="152"/>
+      <c r="R70" s="153"/>
       <c r="S70" s="145"/>
       <c r="T70" s="145"/>
-      <c r="U70" s="170"/>
+      <c r="U70" s="171"/>
     </row>
     <row r="71" spans="1:27">
       <c r="A71" s="129">
@@ -17441,7 +17444,7 @@
       </c>
       <c r="B71" s="17"/>
       <c r="C71" s="17"/>
-      <c r="D71" s="154" t="s">
+      <c r="D71" s="155" t="s">
         <v>261</v>
       </c>
       <c r="E71" s="147">
@@ -17467,20 +17470,20 @@
       <c r="O71" s="145"/>
       <c r="P71" s="146"/>
       <c r="Q71" s="148"/>
-      <c r="R71" s="152"/>
+      <c r="R71" s="153"/>
       <c r="S71" s="145"/>
       <c r="T71" s="145"/>
-      <c r="U71" s="170"/>
+      <c r="U71" s="171"/>
     </row>
     <row r="72" spans="1:27">
       <c r="A72" s="129">
         <v>68</v>
       </c>
       <c r="B72" s="17"/>
-      <c r="C72" s="171" t="s">
+      <c r="C72" s="172" t="s">
         <v>263</v>
       </c>
-      <c r="D72" s="155" t="s">
+      <c r="D72" s="156" t="s">
         <v>264</v>
       </c>
       <c r="E72" s="141">
@@ -17506,10 +17509,10 @@
       <c r="O72" s="145"/>
       <c r="P72" s="146"/>
       <c r="Q72" s="148"/>
-      <c r="R72" s="152"/>
+      <c r="R72" s="153"/>
       <c r="S72" s="145"/>
       <c r="T72" s="145"/>
-      <c r="U72" s="170"/>
+      <c r="U72" s="171"/>
     </row>
     <row r="73" spans="1:27">
       <c r="A73" s="129">
@@ -17517,7 +17520,7 @@
       </c>
       <c r="B73" s="17"/>
       <c r="C73" s="26"/>
-      <c r="D73" s="155" t="s">
+      <c r="D73" s="156" t="s">
         <v>266</v>
       </c>
       <c r="E73" s="141" t="s">
@@ -17543,20 +17546,20 @@
       <c r="O73" s="145"/>
       <c r="P73" s="146"/>
       <c r="Q73" s="148"/>
-      <c r="R73" s="152"/>
+      <c r="R73" s="153"/>
       <c r="S73" s="145"/>
       <c r="T73" s="145"/>
-      <c r="U73" s="170"/>
+      <c r="U73" s="171"/>
     </row>
     <row r="74" spans="1:27">
       <c r="A74" s="129">
         <v>70</v>
       </c>
       <c r="B74" s="17"/>
-      <c r="C74" s="171" t="s">
+      <c r="C74" s="172" t="s">
         <v>269</v>
       </c>
-      <c r="D74" s="155" t="s">
+      <c r="D74" s="156" t="s">
         <v>270</v>
       </c>
       <c r="E74" s="141" t="s">
@@ -17582,10 +17585,10 @@
       <c r="O74" s="145"/>
       <c r="P74" s="146"/>
       <c r="Q74" s="148"/>
-      <c r="R74" s="152"/>
+      <c r="R74" s="153"/>
       <c r="S74" s="145"/>
       <c r="T74" s="145"/>
-      <c r="U74" s="170"/>
+      <c r="U74" s="171"/>
     </row>
     <row r="75" spans="1:27">
       <c r="A75" s="129">
@@ -17593,7 +17596,7 @@
       </c>
       <c r="B75" s="17"/>
       <c r="C75" s="17"/>
-      <c r="D75" s="155" t="s">
+      <c r="D75" s="156" t="s">
         <v>273</v>
       </c>
       <c r="E75" s="141" t="s">
@@ -17619,10 +17622,10 @@
       <c r="O75" s="145"/>
       <c r="P75" s="146"/>
       <c r="Q75" s="148"/>
-      <c r="R75" s="152"/>
+      <c r="R75" s="153"/>
       <c r="S75" s="145"/>
       <c r="T75" s="145"/>
-      <c r="U75" s="170"/>
+      <c r="U75" s="171"/>
     </row>
     <row r="76" spans="1:27">
       <c r="A76" s="129">
@@ -17630,7 +17633,7 @@
       </c>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
-      <c r="D76" s="155" t="s">
+      <c r="D76" s="156" t="s">
         <v>275</v>
       </c>
       <c r="E76" s="141" t="s">
@@ -17656,10 +17659,10 @@
       <c r="O76" s="145"/>
       <c r="P76" s="146"/>
       <c r="Q76" s="148"/>
-      <c r="R76" s="152"/>
+      <c r="R76" s="153"/>
       <c r="S76" s="145"/>
       <c r="T76" s="145"/>
-      <c r="U76" s="170"/>
+      <c r="U76" s="171"/>
     </row>
     <row r="77" spans="1:27">
       <c r="A77" s="129">
@@ -17667,7 +17670,7 @@
       </c>
       <c r="B77" s="17"/>
       <c r="C77" s="26"/>
-      <c r="D77" s="155" t="s">
+      <c r="D77" s="156" t="s">
         <v>277</v>
       </c>
       <c r="E77" s="141" t="s">
@@ -17693,20 +17696,20 @@
       <c r="O77" s="145"/>
       <c r="P77" s="146"/>
       <c r="Q77" s="148"/>
-      <c r="R77" s="152"/>
+      <c r="R77" s="153"/>
       <c r="S77" s="145"/>
       <c r="T77" s="145"/>
-      <c r="U77" s="170"/>
+      <c r="U77" s="171"/>
     </row>
     <row r="78" spans="1:27">
       <c r="A78" s="129">
         <v>74</v>
       </c>
       <c r="B78" s="17"/>
-      <c r="C78" s="171" t="s">
+      <c r="C78" s="172" t="s">
         <v>279</v>
       </c>
-      <c r="D78" s="155" t="s">
+      <c r="D78" s="156" t="s">
         <v>280</v>
       </c>
       <c r="E78" s="141" t="s">
@@ -17732,10 +17735,10 @@
       <c r="O78" s="145"/>
       <c r="P78" s="146"/>
       <c r="Q78" s="148"/>
-      <c r="R78" s="152"/>
+      <c r="R78" s="153"/>
       <c r="S78" s="145"/>
       <c r="T78" s="145"/>
-      <c r="U78" s="170"/>
+      <c r="U78" s="171"/>
     </row>
     <row r="79" spans="1:27">
       <c r="A79" s="129">
@@ -17743,7 +17746,7 @@
       </c>
       <c r="B79" s="17"/>
       <c r="C79" s="26"/>
-      <c r="D79" s="155" t="s">
+      <c r="D79" s="156" t="s">
         <v>283</v>
       </c>
       <c r="E79" s="141" t="s">
@@ -17769,20 +17772,20 @@
       <c r="O79" s="145"/>
       <c r="P79" s="146"/>
       <c r="Q79" s="148"/>
-      <c r="R79" s="152"/>
+      <c r="R79" s="153"/>
       <c r="S79" s="145"/>
       <c r="T79" s="145"/>
-      <c r="U79" s="170"/>
+      <c r="U79" s="171"/>
     </row>
     <row r="80" spans="1:27">
       <c r="A80" s="129">
         <v>76</v>
       </c>
       <c r="B80" s="17"/>
-      <c r="C80" s="171" t="s">
+      <c r="C80" s="172" t="s">
         <v>285</v>
       </c>
-      <c r="D80" s="155" t="s">
+      <c r="D80" s="156" t="s">
         <v>286</v>
       </c>
       <c r="E80" s="141" t="s">
@@ -17808,10 +17811,10 @@
       <c r="O80" s="145"/>
       <c r="P80" s="146"/>
       <c r="Q80" s="148"/>
-      <c r="R80" s="152"/>
+      <c r="R80" s="153"/>
       <c r="S80" s="145"/>
       <c r="T80" s="145"/>
-      <c r="U80" s="170"/>
+      <c r="U80" s="171"/>
     </row>
     <row r="81" spans="1:21">
       <c r="A81" s="129">
@@ -17819,7 +17822,7 @@
       </c>
       <c r="B81" s="17"/>
       <c r="C81" s="17"/>
-      <c r="D81" s="155" t="s">
+      <c r="D81" s="156" t="s">
         <v>288</v>
       </c>
       <c r="E81" s="141" t="s">
@@ -17845,10 +17848,10 @@
       <c r="O81" s="145"/>
       <c r="P81" s="146"/>
       <c r="Q81" s="148"/>
-      <c r="R81" s="152"/>
+      <c r="R81" s="153"/>
       <c r="S81" s="145"/>
       <c r="T81" s="145"/>
-      <c r="U81" s="170"/>
+      <c r="U81" s="171"/>
     </row>
     <row r="82" spans="1:21">
       <c r="A82" s="129">
@@ -17856,7 +17859,7 @@
       </c>
       <c r="B82" s="17"/>
       <c r="C82" s="17"/>
-      <c r="D82" s="155" t="s">
+      <c r="D82" s="156" t="s">
         <v>290</v>
       </c>
       <c r="E82" s="141" t="s">
@@ -17882,10 +17885,10 @@
       <c r="O82" s="145"/>
       <c r="P82" s="146"/>
       <c r="Q82" s="148"/>
-      <c r="R82" s="152"/>
+      <c r="R82" s="153"/>
       <c r="S82" s="145"/>
       <c r="T82" s="145"/>
-      <c r="U82" s="170"/>
+      <c r="U82" s="171"/>
     </row>
     <row r="83" ht="15" customHeight="1" spans="1:21">
       <c r="A83" s="129">
@@ -17893,7 +17896,7 @@
       </c>
       <c r="B83" s="26"/>
       <c r="C83" s="26"/>
-      <c r="D83" s="173" t="s">
+      <c r="D83" s="174" t="s">
         <v>292</v>
       </c>
       <c r="E83" s="34" t="s">
@@ -17915,14 +17918,14 @@
       <c r="M83" s="36">
         <v>-2</v>
       </c>
-      <c r="N83" s="174"/>
+      <c r="N83" s="175"/>
       <c r="O83" s="38"/>
       <c r="P83" s="39"/>
-      <c r="Q83" s="175"/>
-      <c r="R83" s="176"/>
+      <c r="Q83" s="176"/>
+      <c r="R83" s="177"/>
       <c r="S83" s="38"/>
       <c r="T83" s="38"/>
-      <c r="U83" s="177"/>
+      <c r="U83" s="178"/>
     </row>
   </sheetData>
   <mergeCells count="38">
